--- a/quizzes/peinture-19e-niveau3.xlsx
+++ b/quizzes/peinture-19e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E22AA2B-912C-488A-96AD-5C8395B90583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F16184-5AE3-4DB7-8232-4940F4B0E3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1511,9 +1511,6 @@
     <t>Musée des Beaux-Arts, Rouen</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Le Fantôme d’une Puce</t>
   </si>
   <si>
@@ -1755,6 +1752,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Pierre-Auguste_Renoir_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg/960px-William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2350,7 +2350,7 @@
         <v>116</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24.95" customHeight="1">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="28" spans="1:5" ht="24.95" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>8</v>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="33" spans="1:5" ht="24.95" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>156</v>
@@ -2741,7 +2741,7 @@
         <v>104</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24.95" customHeight="1">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="53" spans="1:5" ht="24.95" customHeight="1">
       <c r="A53" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>402</v>
@@ -3081,12 +3081,12 @@
         <v>208</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="24.95" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>402</v>
@@ -3098,7 +3098,7 @@
         <v>98</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="24.95" customHeight="1">
@@ -3256,7 +3256,7 @@
     </row>
     <row r="64" spans="1:5" ht="24.95" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>404</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="65" spans="1:5" ht="24.95" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>404</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="74" spans="1:5" ht="24.95" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>401</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="75" spans="1:5" ht="24.95" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>401</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="91" spans="1:5" ht="24.95" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>106</v>
@@ -3727,7 +3727,7 @@
         <v>355</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="24.95" customHeight="1">
@@ -4140,7 +4140,7 @@
     </row>
     <row r="116" spans="1:5" ht="24.95" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>112</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="119" spans="1:5" ht="24.95" customHeight="1">
       <c r="A119" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>19</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="120" spans="1:5" ht="24.95" customHeight="1">
       <c r="A120" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>19</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="121" spans="1:5" ht="24.95" customHeight="1">
       <c r="A121" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>19</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="122" spans="1:5" ht="24.95" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>19</v>
@@ -4251,10 +4251,10 @@
         <v>1845</v>
       </c>
       <c r="D122" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="E122" s="13" t="s">
         <v>514</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="24.95" customHeight="1">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="124" spans="1:5" ht="24.95" customHeight="1">
       <c r="A124" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>204</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="125" spans="1:5" ht="24.95" customHeight="1">
       <c r="A125" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>204</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="126" spans="1:5" ht="24.95" customHeight="1">
       <c r="A126" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>204</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="127" spans="1:5" ht="24.95" customHeight="1">
       <c r="A127" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>204</v>
@@ -4339,7 +4339,7 @@
         <v>104</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="24.95" customHeight="1">
@@ -4361,7 +4361,7 @@
     </row>
     <row r="129" spans="1:5" ht="24.95" customHeight="1">
       <c r="A129" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>24</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="130" spans="1:5" ht="24.95" customHeight="1">
       <c r="A130" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>24</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="132" spans="1:5" ht="24.95" customHeight="1">
       <c r="A132" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>231</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="133" spans="1:5" ht="24.95" customHeight="1">
       <c r="A133" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>231</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="134" spans="1:5" ht="24.95" customHeight="1">
       <c r="A134" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>228</v>
@@ -4458,12 +4458,12 @@
         <v>208</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="24.95" customHeight="1">
       <c r="A135" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>228</v>
@@ -4475,7 +4475,7 @@
         <v>104</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="24.95" customHeight="1">
@@ -4650,7 +4650,7 @@
     </row>
     <row r="146" spans="1:5" ht="24.95" customHeight="1">
       <c r="A146" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B146" s="9" t="s">
         <v>397</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="149" spans="1:5" ht="24.95" customHeight="1">
       <c r="A149" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>399</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="150" spans="1:5" ht="24.95" customHeight="1">
       <c r="A150" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B150" s="9" t="s">
         <v>399</v>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="151" spans="1:5" ht="24.95" customHeight="1">
       <c r="A151" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>232</v>
@@ -4747,12 +4747,12 @@
         <v>104</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="24.95" customHeight="1">
       <c r="A152" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B152" s="9" t="s">
         <v>232</v>
@@ -4764,7 +4764,7 @@
         <v>104</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="24.95" customHeight="1">
@@ -4803,13 +4803,13 @@
     </row>
     <row r="155" spans="1:5" ht="24.95" customHeight="1">
       <c r="A155" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B155" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D155" s="9" t="s">
         <v>208</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="158" spans="1:5" ht="24.95" customHeight="1">
       <c r="A158" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B158" s="9" t="s">
         <v>17</v>
@@ -4866,12 +4866,12 @@
         <v>167</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="24.95" customHeight="1">
       <c r="A159" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B159" s="9" t="s">
         <v>17</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="163" spans="1:5" ht="24.95" customHeight="1">
       <c r="A163" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B163" s="9" t="s">
         <v>13</v>
@@ -4951,12 +4951,12 @@
         <v>104</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="24.95" customHeight="1">
       <c r="A164" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B164" s="9" t="s">
         <v>13</v>
@@ -4965,15 +4965,15 @@
         <v>1889</v>
       </c>
       <c r="D164" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E164" s="9" t="s">
         <v>504</v>
-      </c>
-      <c r="E164" s="9" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="24.95" customHeight="1">
       <c r="A165" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B165" s="9" t="s">
         <v>13</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="166" spans="1:5" ht="24.95" customHeight="1">
       <c r="A166" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B166" s="9" t="s">
         <v>398</v>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="171" spans="1:5" ht="24.95" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B171" s="9" t="s">
         <v>119</v>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="174" spans="1:5" ht="24.95" customHeight="1">
       <c r="A174" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B174" s="9" t="s">
         <v>119</v>
@@ -5138,7 +5138,7 @@
         <v>104</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="24.95" customHeight="1">
@@ -5160,7 +5160,7 @@
     </row>
     <row r="176" spans="1:5" ht="24.95" customHeight="1">
       <c r="A176" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B176" s="9" t="s">
         <v>233</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="177" spans="1:5" ht="24.95" customHeight="1">
       <c r="A177" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B177" s="9" t="s">
         <v>233</v>
@@ -5189,7 +5189,7 @@
         <v>104</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="24.95" customHeight="1">
@@ -5228,7 +5228,7 @@
     </row>
     <row r="180" spans="1:5" ht="24.95" customHeight="1">
       <c r="A180" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B180" s="9" t="s">
         <v>229</v>
@@ -5240,12 +5240,12 @@
         <v>104</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="24.95" customHeight="1">
       <c r="A181" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B181" s="9" t="s">
         <v>229</v>
@@ -5257,7 +5257,7 @@
         <v>104</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="24.95" customHeight="1">
@@ -5296,7 +5296,7 @@
     </row>
     <row r="184" spans="1:5" ht="24.95" customHeight="1">
       <c r="A184" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B184" s="9" t="s">
         <v>22</v>
@@ -5308,12 +5308,12 @@
         <v>85</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="24.95" customHeight="1">
       <c r="A185" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B185" s="9" t="s">
         <v>230</v>
@@ -5325,29 +5325,29 @@
         <v>85</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="24.95" customHeight="1">
       <c r="A186" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B186" s="9" t="s">
         <v>230</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D186" s="9" t="s">
         <v>85</v>
       </c>
       <c r="E186" s="14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="24.95" customHeight="1">
       <c r="A187" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B187" s="9" t="s">
         <v>223</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="188" spans="1:5" ht="24.95" customHeight="1">
       <c r="A188" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B188" s="9" t="s">
         <v>223</v>
@@ -5376,7 +5376,7 @@
         <v>208</v>
       </c>
       <c r="E188" s="14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="24.95" customHeight="1">
@@ -5398,7 +5398,7 @@
     </row>
     <row r="190" spans="1:5" ht="24.95" customHeight="1">
       <c r="A190" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>175</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="192" spans="1:5" ht="24.95" customHeight="1">
       <c r="A192" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>126</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="193" spans="1:5" ht="24.95" customHeight="1">
       <c r="A193" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>126</v>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="194" spans="1:5" ht="24.95" customHeight="1">
       <c r="A194" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>126</v>
@@ -5500,7 +5500,7 @@
     </row>
     <row r="196" spans="1:5" ht="24.95" customHeight="1">
       <c r="A196" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>126</v>
@@ -5534,7 +5534,7 @@
     </row>
     <row r="198" spans="1:5" ht="24.95" customHeight="1">
       <c r="A198" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>222</v>
@@ -5550,8 +5550,8 @@
       </c>
     </row>
     <row r="199" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A199" s="10" t="s">
-        <v>492</v>
+      <c r="A199" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="B199" s="9" t="s">
         <v>222</v>
@@ -5563,7 +5563,7 @@
         <v>98</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="24.95" customHeight="1">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="201" spans="1:5" ht="24.95" customHeight="1">
       <c r="A201" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>195</v>
@@ -5720,62 +5720,62 @@
     <hyperlink ref="A173" r:id="rId110" xr:uid="{C47A9AD4-AAFE-4676-BB75-F8B7875D0292}"/>
     <hyperlink ref="A175" r:id="rId111" xr:uid="{59C9109A-9930-44E7-84E6-0F0168DE21E2}"/>
     <hyperlink ref="A168" r:id="rId112" xr:uid="{68879F54-FCFF-4F42-80DE-E528F3616152}"/>
-    <hyperlink ref="A199" r:id="rId113" xr:uid="{E0EB0B7F-86C5-489B-9B1E-30F4CD1285BD}"/>
-    <hyperlink ref="A184" r:id="rId114" xr:uid="{DCEBA736-B0C0-477C-B9F4-0A545D66F544}"/>
-    <hyperlink ref="A33" r:id="rId115" xr:uid="{C648AF0E-3F8C-45DE-A245-E9F999B474E7}"/>
-    <hyperlink ref="A174" r:id="rId116" xr:uid="{31572606-6E7E-4402-A56F-DC2A774D7F8B}"/>
-    <hyperlink ref="A163" r:id="rId117" xr:uid="{35B9E065-14F2-4C72-9F10-F39AAF5B08C1}"/>
-    <hyperlink ref="A164" r:id="rId118" xr:uid="{24FEACB2-49C4-4FF2-A374-6C4E872F80D6}"/>
-    <hyperlink ref="A158" r:id="rId119" xr:uid="{0535AE13-F3EB-4524-8AB4-EED7AFDD8290}"/>
-    <hyperlink ref="A159" r:id="rId120" xr:uid="{2760497A-C96F-4AC8-A408-43AB6BC38045}"/>
-    <hyperlink ref="A155" r:id="rId121" xr:uid="{6C998F41-8AC1-4E6E-8272-EB5732B24642}"/>
-    <hyperlink ref="A91" r:id="rId122" xr:uid="{EB11DE3D-7A29-4096-A813-153AD3DB5E6D}"/>
-    <hyperlink ref="A122" r:id="rId123" xr:uid="{041E876A-2433-410C-86DB-D165BC361D31}"/>
-    <hyperlink ref="A53" r:id="rId124" xr:uid="{D4C842D8-7531-4A74-8F1F-A947139F1601}"/>
-    <hyperlink ref="A54" r:id="rId125" xr:uid="{1BF5D58E-54AE-486A-BD29-CF711430E973}"/>
-    <hyperlink ref="A50" r:id="rId126" xr:uid="{80A29311-12F4-4C45-8A4C-3488C39B58C7}"/>
-    <hyperlink ref="A64" r:id="rId127" xr:uid="{AEDB13FF-A7DA-4323-B1E6-09DC7D6F52AD}"/>
-    <hyperlink ref="A65" r:id="rId128" xr:uid="{AC153A56-094F-40CA-9C34-B370C3CDDE3E}"/>
-    <hyperlink ref="A74" r:id="rId129" xr:uid="{39DF16D9-7950-4B4C-B11C-ED220E9ED900}"/>
-    <hyperlink ref="A75" r:id="rId130" xr:uid="{797D739E-5C5F-4542-8820-F9834995F0AD}"/>
-    <hyperlink ref="A116" r:id="rId131" xr:uid="{6F856887-E47E-4CB0-9C85-A218DBFB5DED}"/>
-    <hyperlink ref="A119" r:id="rId132" xr:uid="{7D676F77-24B9-45C2-93FD-F7FAF131652C}"/>
-    <hyperlink ref="A120" r:id="rId133" xr:uid="{B034BA44-6629-4967-B232-98FB9F925589}"/>
-    <hyperlink ref="A121" r:id="rId134" xr:uid="{E5F4519A-2CCC-4F1E-8240-9A2B5B0994B9}"/>
-    <hyperlink ref="A124" r:id="rId135" xr:uid="{AF524A54-1145-4830-B342-D2569783576A}"/>
-    <hyperlink ref="A125" r:id="rId136" xr:uid="{C2CA6923-410F-4C40-9AD4-C302E9BAE0B7}"/>
-    <hyperlink ref="A126" r:id="rId137" xr:uid="{8B883F8B-D2A3-41CC-A620-C6CE47E6341C}"/>
-    <hyperlink ref="A127" r:id="rId138" xr:uid="{53D032C4-EA6A-4FB8-AA61-59597AB575CE}"/>
-    <hyperlink ref="A129" r:id="rId139" xr:uid="{D51B6DCD-99CE-44E0-9D44-4068C962DECE}"/>
-    <hyperlink ref="A130" r:id="rId140" xr:uid="{DE7F2DFC-ED2C-4A26-8444-F09C51CEB758}"/>
-    <hyperlink ref="A132" r:id="rId141" xr:uid="{E67C22F8-B77A-49F6-8AD5-7F1784A467B4}"/>
-    <hyperlink ref="A133" r:id="rId142" xr:uid="{63D27158-9E6E-4E69-8ACC-D1CB72F83C17}"/>
-    <hyperlink ref="A134" r:id="rId143" xr:uid="{FB89F716-51C5-488C-933F-97A56D626EDF}"/>
-    <hyperlink ref="A146" r:id="rId144" xr:uid="{4B039211-FE10-4875-94B7-BEF2C348B8B2}"/>
-    <hyperlink ref="A151" r:id="rId145" xr:uid="{D6FD384D-F923-4D96-8FE5-6C9A3BA2A839}"/>
-    <hyperlink ref="A152" r:id="rId146" xr:uid="{9AE596AD-8DFA-40E4-B677-1E121F22AC4C}"/>
-    <hyperlink ref="A149" r:id="rId147" xr:uid="{306BFBD8-DE2D-4860-8F2A-35D7F9211288}"/>
-    <hyperlink ref="A150" r:id="rId148" display="https://upload.wikimedia.org/wikipedia/commons/d/d4/Mikhail_Vrubel_-_%D0%9F%D1%80%D0%B8%D0%BD%D1%86%D0%B5%D1%81%D1%81%D0%B0_%D0%93%D1%80%D1%91%D0%B7%D0%B0_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original" xr:uid="{5744E552-17D1-4FE6-8FE4-6AFBE58BFF17}"/>
-    <hyperlink ref="A165" r:id="rId149" xr:uid="{E03F017A-1225-455A-9D90-9D10A2B2B824}"/>
-    <hyperlink ref="A166" r:id="rId150" xr:uid="{3579996B-2E23-43FC-BDD4-1C0FAA549F80}"/>
-    <hyperlink ref="A176" r:id="rId151" xr:uid="{ACD00D1E-5FFA-4FA9-ABE7-A89DA6F5EA6B}"/>
-    <hyperlink ref="A177" r:id="rId152" xr:uid="{EAAD252B-D3E2-411A-B3C5-E6D70A712BA7}"/>
-    <hyperlink ref="A180" r:id="rId153" xr:uid="{036A0429-A70A-4779-A15B-991768F6DDB1}"/>
-    <hyperlink ref="A181" r:id="rId154" xr:uid="{82F37061-53B8-4FCC-A2C3-27AA31CDE286}"/>
-    <hyperlink ref="A185" r:id="rId155" xr:uid="{AA871925-A2DF-4C8A-9900-F0115E306F4E}"/>
-    <hyperlink ref="A186" r:id="rId156" xr:uid="{BCED48E8-4D4F-4BB8-B008-6820D6F8575E}"/>
-    <hyperlink ref="A187" r:id="rId157" xr:uid="{F4501C77-5F34-4091-B3F1-E0690F55C64A}"/>
-    <hyperlink ref="A188" r:id="rId158" xr:uid="{BA3CE526-5700-4DB3-99D1-5BF71B20D2A0}"/>
-    <hyperlink ref="A201" r:id="rId159" xr:uid="{88D6C944-9B1A-4FA0-9EE8-37335137C8EE}"/>
-    <hyperlink ref="A193" r:id="rId160" xr:uid="{253BB352-A38A-4BCF-A3B9-AFEDB8A6FAA1}"/>
-    <hyperlink ref="A194" r:id="rId161" xr:uid="{9F4CC163-7009-442F-AC2E-4C666F4B7394}"/>
-    <hyperlink ref="A196" r:id="rId162" xr:uid="{23A37191-5CF7-4300-9679-A4DEFDBF7D0C}"/>
-    <hyperlink ref="A190" r:id="rId163" xr:uid="{9C6623C3-5C47-489A-A43C-2F3C91051653}"/>
-    <hyperlink ref="A198" r:id="rId164" xr:uid="{3F0992ED-5E04-4B57-B62D-16F2205B2E06}"/>
-    <hyperlink ref="A135" r:id="rId165" xr:uid="{10D5EF7A-C9FD-4E0B-9D4F-11546AF1D6FA}"/>
-    <hyperlink ref="A192" r:id="rId166" xr:uid="{9C5FE215-A90A-4FA3-8791-5B53865D684A}"/>
-    <hyperlink ref="A28" r:id="rId167" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg/1280px-Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C77C0BD-A435-4463-B4D4-AA8E1FC32944}"/>
-    <hyperlink ref="A171" r:id="rId168" xr:uid="{6CAEC4BE-2398-4C4A-9114-BE3B69F90F24}"/>
+    <hyperlink ref="A184" r:id="rId113" xr:uid="{DCEBA736-B0C0-477C-B9F4-0A545D66F544}"/>
+    <hyperlink ref="A33" r:id="rId114" xr:uid="{C648AF0E-3F8C-45DE-A245-E9F999B474E7}"/>
+    <hyperlink ref="A174" r:id="rId115" xr:uid="{31572606-6E7E-4402-A56F-DC2A774D7F8B}"/>
+    <hyperlink ref="A163" r:id="rId116" xr:uid="{35B9E065-14F2-4C72-9F10-F39AAF5B08C1}"/>
+    <hyperlink ref="A164" r:id="rId117" xr:uid="{24FEACB2-49C4-4FF2-A374-6C4E872F80D6}"/>
+    <hyperlink ref="A158" r:id="rId118" xr:uid="{0535AE13-F3EB-4524-8AB4-EED7AFDD8290}"/>
+    <hyperlink ref="A159" r:id="rId119" xr:uid="{2760497A-C96F-4AC8-A408-43AB6BC38045}"/>
+    <hyperlink ref="A155" r:id="rId120" xr:uid="{6C998F41-8AC1-4E6E-8272-EB5732B24642}"/>
+    <hyperlink ref="A91" r:id="rId121" xr:uid="{EB11DE3D-7A29-4096-A813-153AD3DB5E6D}"/>
+    <hyperlink ref="A122" r:id="rId122" xr:uid="{041E876A-2433-410C-86DB-D165BC361D31}"/>
+    <hyperlink ref="A53" r:id="rId123" xr:uid="{D4C842D8-7531-4A74-8F1F-A947139F1601}"/>
+    <hyperlink ref="A54" r:id="rId124" xr:uid="{1BF5D58E-54AE-486A-BD29-CF711430E973}"/>
+    <hyperlink ref="A50" r:id="rId125" xr:uid="{80A29311-12F4-4C45-8A4C-3488C39B58C7}"/>
+    <hyperlink ref="A64" r:id="rId126" xr:uid="{AEDB13FF-A7DA-4323-B1E6-09DC7D6F52AD}"/>
+    <hyperlink ref="A65" r:id="rId127" xr:uid="{AC153A56-094F-40CA-9C34-B370C3CDDE3E}"/>
+    <hyperlink ref="A74" r:id="rId128" xr:uid="{39DF16D9-7950-4B4C-B11C-ED220E9ED900}"/>
+    <hyperlink ref="A75" r:id="rId129" xr:uid="{797D739E-5C5F-4542-8820-F9834995F0AD}"/>
+    <hyperlink ref="A116" r:id="rId130" xr:uid="{6F856887-E47E-4CB0-9C85-A218DBFB5DED}"/>
+    <hyperlink ref="A119" r:id="rId131" xr:uid="{7D676F77-24B9-45C2-93FD-F7FAF131652C}"/>
+    <hyperlink ref="A120" r:id="rId132" xr:uid="{B034BA44-6629-4967-B232-98FB9F925589}"/>
+    <hyperlink ref="A121" r:id="rId133" xr:uid="{E5F4519A-2CCC-4F1E-8240-9A2B5B0994B9}"/>
+    <hyperlink ref="A124" r:id="rId134" xr:uid="{AF524A54-1145-4830-B342-D2569783576A}"/>
+    <hyperlink ref="A125" r:id="rId135" xr:uid="{C2CA6923-410F-4C40-9AD4-C302E9BAE0B7}"/>
+    <hyperlink ref="A126" r:id="rId136" xr:uid="{8B883F8B-D2A3-41CC-A620-C6CE47E6341C}"/>
+    <hyperlink ref="A127" r:id="rId137" xr:uid="{53D032C4-EA6A-4FB8-AA61-59597AB575CE}"/>
+    <hyperlink ref="A129" r:id="rId138" xr:uid="{D51B6DCD-99CE-44E0-9D44-4068C962DECE}"/>
+    <hyperlink ref="A130" r:id="rId139" xr:uid="{DE7F2DFC-ED2C-4A26-8444-F09C51CEB758}"/>
+    <hyperlink ref="A132" r:id="rId140" xr:uid="{E67C22F8-B77A-49F6-8AD5-7F1784A467B4}"/>
+    <hyperlink ref="A133" r:id="rId141" xr:uid="{63D27158-9E6E-4E69-8ACC-D1CB72F83C17}"/>
+    <hyperlink ref="A134" r:id="rId142" xr:uid="{FB89F716-51C5-488C-933F-97A56D626EDF}"/>
+    <hyperlink ref="A146" r:id="rId143" xr:uid="{4B039211-FE10-4875-94B7-BEF2C348B8B2}"/>
+    <hyperlink ref="A151" r:id="rId144" xr:uid="{D6FD384D-F923-4D96-8FE5-6C9A3BA2A839}"/>
+    <hyperlink ref="A152" r:id="rId145" xr:uid="{9AE596AD-8DFA-40E4-B677-1E121F22AC4C}"/>
+    <hyperlink ref="A149" r:id="rId146" xr:uid="{306BFBD8-DE2D-4860-8F2A-35D7F9211288}"/>
+    <hyperlink ref="A150" r:id="rId147" display="https://upload.wikimedia.org/wikipedia/commons/d/d4/Mikhail_Vrubel_-_%D0%9F%D1%80%D0%B8%D0%BD%D1%86%D0%B5%D1%81%D1%81%D0%B0_%D0%93%D1%80%D1%91%D0%B7%D0%B0_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original" xr:uid="{5744E552-17D1-4FE6-8FE4-6AFBE58BFF17}"/>
+    <hyperlink ref="A165" r:id="rId148" xr:uid="{E03F017A-1225-455A-9D90-9D10A2B2B824}"/>
+    <hyperlink ref="A166" r:id="rId149" xr:uid="{3579996B-2E23-43FC-BDD4-1C0FAA549F80}"/>
+    <hyperlink ref="A176" r:id="rId150" xr:uid="{ACD00D1E-5FFA-4FA9-ABE7-A89DA6F5EA6B}"/>
+    <hyperlink ref="A177" r:id="rId151" xr:uid="{EAAD252B-D3E2-411A-B3C5-E6D70A712BA7}"/>
+    <hyperlink ref="A180" r:id="rId152" xr:uid="{036A0429-A70A-4779-A15B-991768F6DDB1}"/>
+    <hyperlink ref="A181" r:id="rId153" xr:uid="{82F37061-53B8-4FCC-A2C3-27AA31CDE286}"/>
+    <hyperlink ref="A185" r:id="rId154" xr:uid="{AA871925-A2DF-4C8A-9900-F0115E306F4E}"/>
+    <hyperlink ref="A186" r:id="rId155" xr:uid="{BCED48E8-4D4F-4BB8-B008-6820D6F8575E}"/>
+    <hyperlink ref="A187" r:id="rId156" xr:uid="{F4501C77-5F34-4091-B3F1-E0690F55C64A}"/>
+    <hyperlink ref="A188" r:id="rId157" xr:uid="{BA3CE526-5700-4DB3-99D1-5BF71B20D2A0}"/>
+    <hyperlink ref="A201" r:id="rId158" xr:uid="{88D6C944-9B1A-4FA0-9EE8-37335137C8EE}"/>
+    <hyperlink ref="A193" r:id="rId159" xr:uid="{253BB352-A38A-4BCF-A3B9-AFEDB8A6FAA1}"/>
+    <hyperlink ref="A194" r:id="rId160" xr:uid="{9F4CC163-7009-442F-AC2E-4C666F4B7394}"/>
+    <hyperlink ref="A196" r:id="rId161" xr:uid="{23A37191-5CF7-4300-9679-A4DEFDBF7D0C}"/>
+    <hyperlink ref="A190" r:id="rId162" xr:uid="{9C6623C3-5C47-489A-A43C-2F3C91051653}"/>
+    <hyperlink ref="A198" r:id="rId163" xr:uid="{3F0992ED-5E04-4B57-B62D-16F2205B2E06}"/>
+    <hyperlink ref="A135" r:id="rId164" xr:uid="{10D5EF7A-C9FD-4E0B-9D4F-11546AF1D6FA}"/>
+    <hyperlink ref="A192" r:id="rId165" xr:uid="{9C5FE215-A90A-4FA3-8791-5B53865D684A}"/>
+    <hyperlink ref="A28" r:id="rId166" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg/1280px-Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C77C0BD-A435-4463-B4D4-AA8E1FC32944}"/>
+    <hyperlink ref="A171" r:id="rId167" xr:uid="{6CAEC4BE-2398-4C4A-9114-BE3B69F90F24}"/>
+    <hyperlink ref="A199" r:id="rId168" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg/960px-William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21CB91A6-C5D0-49FE-92F5-955C1A824528}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
